--- a/rmonize/data_proc_elem/DPE_BGS98_P2.xlsx
+++ b/rmonize/data_proc_elem/DPE_BGS98_P2.xlsx
@@ -687,17 +687,19 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MIausl</t>
+          <t>MIlandB;MIstaat_m1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>recode</t>
+          <t>case_when</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>recode(1=1;2=0)</t>
+          <t>case_when(is.na(MIlandB) ~ 1,_x000D_
+          is.na(MIstaat_m1) ~ 1,_x000D_
+          TRUE ~ 0)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -4015,24 +4017,29 @@
           <t>BGS98_P2</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AGE_ANTH_FUP</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4360,24 +4367,29 @@
           <t>BGS98_P2</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>GFS</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>direct_mapping</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
@@ -4405,24 +4417,34 @@
           <t>BGS98_P2</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>GFU;GFP</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>operation</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>GFU-GFP</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Total unsaturated fatty acids - polyunsaturated fatty acids</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>compatible</t>
         </is>
       </c>
     </row>
@@ -4500,24 +4522,34 @@
           <t>BGS98_P2</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>GKD;GKM</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>operation</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>GKD+GKM</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Total sugars (monosaccharides + disaccharides)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>impossible</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>unavailable</t>
+          <t>compatible</t>
         </is>
       </c>
     </row>
